--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-06-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A0527B-645D-43E8-8B15-F7C50E713236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CE362E-B0A3-4D0A-AE1D-8CF456DC16E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32445" yWindow="1755" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33105" yWindow="1125" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="398">
   <si>
     <t>SKU</t>
   </si>
@@ -1078,57 +1078,15 @@
     <t>£2265.12</t>
   </si>
   <si>
-    <t>£15.75</t>
-  </si>
-  <si>
-    <t>£23.25</t>
-  </si>
-  <si>
-    <t>£23.50</t>
-  </si>
-  <si>
-    <t>£30.50</t>
-  </si>
-  <si>
-    <t>£37.00</t>
-  </si>
-  <si>
-    <t>£40.75</t>
-  </si>
-  <si>
-    <t>£39.92</t>
-  </si>
-  <si>
-    <t>£49.75</t>
-  </si>
-  <si>
     <t>£61.50</t>
   </si>
   <si>
-    <t>£60.50</t>
-  </si>
-  <si>
-    <t>£1,095.00</t>
-  </si>
-  <si>
-    <t>£1,295.00</t>
-  </si>
-  <si>
     <t>£51.75</t>
   </si>
   <si>
     <t>£64.75</t>
   </si>
   <si>
-    <t>£69.75</t>
-  </si>
-  <si>
-    <t>£65.50</t>
-  </si>
-  <si>
-    <t>£1,745.00</t>
-  </si>
-  <si>
     <t>£2,050.00</t>
   </si>
   <si>
@@ -1202,6 +1160,60 @@
   </si>
   <si>
     <t>£2655.52</t>
+  </si>
+  <si>
+    <t>£17.00</t>
+  </si>
+  <si>
+    <t>£19.50</t>
+  </si>
+  <si>
+    <t>£24.50</t>
+  </si>
+  <si>
+    <t>£24.75</t>
+  </si>
+  <si>
+    <t>£31.75</t>
+  </si>
+  <si>
+    <t>£34.75</t>
+  </si>
+  <si>
+    <t>£39.00</t>
+  </si>
+  <si>
+    <t>£42.00</t>
+  </si>
+  <si>
+    <t>£42.75</t>
+  </si>
+  <si>
+    <t>£55.00</t>
+  </si>
+  <si>
+    <t>£65.75</t>
+  </si>
+  <si>
+    <t>£64.00</t>
+  </si>
+  <si>
+    <t>£1,125.00</t>
+  </si>
+  <si>
+    <t>£1,350.00</t>
+  </si>
+  <si>
+    <t>£71.25</t>
+  </si>
+  <si>
+    <t>£75.00</t>
+  </si>
+  <si>
+    <t>£72.50</t>
+  </si>
+  <si>
+    <t>£1,855.00</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1652,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -1664,7 +1676,7 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
@@ -1696,7 +1708,7 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>381</v>
       </c>
       <c r="G3" t="s">
         <v>34</v>
@@ -1720,7 +1732,7 @@
         <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="O3" t="s">
         <v>40</v>
@@ -1752,7 +1764,7 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="G4" t="s">
         <v>47</v>
@@ -1776,7 +1788,7 @@
         <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="O4" t="s">
         <v>53</v>
@@ -1808,7 +1820,7 @@
         <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="G5" t="s">
         <v>60</v>
@@ -1832,7 +1844,7 @@
         <v>65</v>
       </c>
       <c r="N5" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="O5" t="s">
         <v>66</v>
@@ -1864,7 +1876,7 @@
         <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="G6" t="s">
         <v>73</v>
@@ -1888,7 +1900,7 @@
         <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="O6" t="s">
         <v>79</v>
@@ -1920,7 +1932,7 @@
         <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="G7" t="s">
         <v>85</v>
@@ -1944,7 +1956,7 @@
         <v>90</v>
       </c>
       <c r="N7" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="O7" t="s">
         <v>91</v>
@@ -1976,7 +1988,7 @@
         <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="G8" t="s">
         <v>85</v>
@@ -2000,7 +2012,7 @@
         <v>101</v>
       </c>
       <c r="N8" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="O8" t="s">
         <v>102</v>
@@ -2032,7 +2044,7 @@
         <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="G9" t="s">
         <v>109</v>
@@ -2056,7 +2068,7 @@
         <v>114</v>
       </c>
       <c r="N9" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="O9" t="s">
         <v>115</v>
@@ -2088,7 +2100,7 @@
         <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="G10" t="s">
         <v>122</v>
@@ -2112,7 +2124,7 @@
         <v>127</v>
       </c>
       <c r="N10" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="O10" t="s">
         <v>128</v>
@@ -2144,7 +2156,7 @@
         <v>134</v>
       </c>
       <c r="F11" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="G11" t="s">
         <v>135</v>
@@ -2168,7 +2180,7 @@
         <v>139</v>
       </c>
       <c r="N11" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="O11" t="s">
         <v>140</v>
@@ -2200,7 +2212,7 @@
         <v>146</v>
       </c>
       <c r="F12" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="G12" t="s">
         <v>146</v>
@@ -2224,7 +2236,7 @@
         <v>151</v>
       </c>
       <c r="N12" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="O12" t="s">
         <v>146</v>
@@ -2256,7 +2268,7 @@
         <v>156</v>
       </c>
       <c r="F13" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="G13" t="s">
         <v>157</v>
@@ -2280,7 +2292,7 @@
         <v>162</v>
       </c>
       <c r="N13" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="O13" t="s">
         <v>163</v>
@@ -2312,7 +2324,7 @@
         <v>169</v>
       </c>
       <c r="F14" t="s">
-        <v>169</v>
+        <v>354</v>
       </c>
       <c r="G14" t="s">
         <v>170</v>
@@ -2336,7 +2348,7 @@
         <v>175</v>
       </c>
       <c r="N14" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="O14" t="s">
         <v>176</v>
@@ -2368,7 +2380,7 @@
         <v>147</v>
       </c>
       <c r="F15" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="G15" t="s">
         <v>183</v>
@@ -2424,7 +2436,7 @@
         <v>194</v>
       </c>
       <c r="F16" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="G16" t="s">
         <v>195</v>
@@ -2448,7 +2460,7 @@
         <v>200</v>
       </c>
       <c r="N16" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="O16" t="s">
         <v>201</v>
@@ -2480,7 +2492,7 @@
         <v>207</v>
       </c>
       <c r="F17" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="G17" t="s">
         <v>147</v>
@@ -2504,7 +2516,7 @@
         <v>211</v>
       </c>
       <c r="N17" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="O17" t="s">
         <v>212</v>
@@ -2536,7 +2548,7 @@
         <v>217</v>
       </c>
       <c r="F18" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="G18" t="s">
         <v>218</v>
@@ -2560,7 +2572,7 @@
         <v>223</v>
       </c>
       <c r="N18" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="O18" t="s">
         <v>224</v>
@@ -2592,7 +2604,7 @@
         <v>230</v>
       </c>
       <c r="F19" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="G19" t="s">
         <v>231</v>
@@ -2616,7 +2628,7 @@
         <v>236</v>
       </c>
       <c r="N19" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="O19" t="s">
         <v>237</v>
@@ -2648,7 +2660,7 @@
         <v>243</v>
       </c>
       <c r="F20" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="G20" t="s">
         <v>244</v>
@@ -2672,7 +2684,7 @@
         <v>248</v>
       </c>
       <c r="N20" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="O20" t="s">
         <v>249</v>
@@ -2704,7 +2716,7 @@
         <v>255</v>
       </c>
       <c r="F21" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="G21" t="s">
         <v>256</v>
@@ -2728,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="N21" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="O21" t="s">
         <v>262</v>
@@ -2760,7 +2772,7 @@
         <v>268</v>
       </c>
       <c r="F22" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="G22" t="s">
         <v>269</v>
@@ -2784,7 +2796,7 @@
         <v>274</v>
       </c>
       <c r="N22" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="O22" t="s">
         <v>275</v>
@@ -2816,7 +2828,7 @@
         <v>259</v>
       </c>
       <c r="F23" t="s">
-        <v>259</v>
+        <v>395</v>
       </c>
       <c r="G23" t="s">
         <v>147</v>
@@ -2840,7 +2852,7 @@
         <v>284</v>
       </c>
       <c r="N23" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="O23" t="s">
         <v>285</v>
@@ -2872,7 +2884,7 @@
         <v>291</v>
       </c>
       <c r="F24" t="s">
-        <v>259</v>
+        <v>396</v>
       </c>
       <c r="G24" t="s">
         <v>147</v>
@@ -2896,7 +2908,7 @@
         <v>296</v>
       </c>
       <c r="N24" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="O24" t="s">
         <v>297</v>
@@ -2984,7 +2996,7 @@
         <v>310</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="G26" t="s">
         <v>147</v>
@@ -3008,7 +3020,7 @@
         <v>315</v>
       </c>
       <c r="N26" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="O26" t="s">
         <v>316</v>
@@ -3040,7 +3052,7 @@
         <v>322</v>
       </c>
       <c r="F27" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="G27" t="s">
         <v>147</v>
@@ -3064,7 +3076,7 @@
         <v>326</v>
       </c>
       <c r="N27" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="O27" t="s">
         <v>327</v>
@@ -3096,7 +3108,7 @@
         <v>333</v>
       </c>
       <c r="F28" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="G28" t="s">
         <v>147</v>
@@ -3120,7 +3132,7 @@
         <v>337</v>
       </c>
       <c r="N28" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="O28" t="s">
         <v>338</v>
@@ -3152,7 +3164,7 @@
         <v>344</v>
       </c>
       <c r="F29" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="G29" t="s">
         <v>147</v>
@@ -3176,7 +3188,7 @@
         <v>348</v>
       </c>
       <c r="N29" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="O29" t="s">
         <v>349</v>
